--- a/InputData/io-model/ACTR/Avg Corp Tax Rate.xlsx
+++ b/InputData/io-model/ACTR/Avg Corp Tax Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\io-model\ACTR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\kjh_local\NEXTgroup_local\2025_local\2. EPS\업데이트 파일\eps-southkorea-3.3.1_2025update_v4.0.3\InputData\io-model\ACTR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6361653D-74BA-485C-9BF1-04243361AEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D53E85B-821F-4D47-9A2C-A9AA2BC867FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Source:</t>
   </si>
@@ -45,15 +45,6 @@
     <t>ACTR Average Corporate Tax Rate</t>
   </si>
   <si>
-    <t>Peter Peterson Foundation</t>
-  </si>
-  <si>
-    <t>The US Corporate Tax System Explained</t>
-  </si>
-  <si>
-    <t>https://www.pgpf.org/budget-basics/the-us-corporate-tax-system-explained</t>
-  </si>
-  <si>
     <t>Combined federal and state corporate tax rate</t>
   </si>
   <si>
@@ -64,17 +55,35 @@
   </si>
   <si>
     <t>Tax Rate</t>
+  </si>
+  <si>
+    <t>https://www.nts.go.kr/nts/cm/cntnts/cntntsView.do?mi=2370&amp;cntntsId=7744</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>South Korea Corporate Tax System Explained</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>국세청</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.taxwatch.co.kr/article/tax/2022/10/11/0001</t>
+  </si>
+  <si>
+    <t>https://www.etoday.co.kr/news/view/2331214</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -82,7 +91,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -90,7 +99,21 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -116,17 +139,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -428,8 +452,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -441,42 +465,56 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>6</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>7</v>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{E8B4439A-6F6F-489E-8CB3-A2E681B3BC48}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -486,23 +524,23 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="26.21875" customWidth="1"/>
+    <col min="2" max="2" width="26.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1">
+        <v>5</v>
+      </c>
+      <c r="B1" s="4">
         <v>2021</v>
       </c>
       <c r="C1">
         <v>2022</v>
       </c>
-      <c r="D1">
+      <c r="D1" s="4">
         <v>2023</v>
       </c>
       <c r="E1">
@@ -589,129 +627,300 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2">
-        <v>0.26</v>
+        <v>6</v>
+      </c>
+      <c r="B2" s="4">
+        <v>0.27500000000000002</v>
       </c>
       <c r="C2">
         <f>$B$2</f>
-        <v>0.26</v>
-      </c>
-      <c r="D2">
-        <f>$B$2</f>
-        <v>0.26</v>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.26400000000000001</v>
       </c>
       <c r="E2">
-        <f t="shared" ref="E2:O2" si="0">$B$2</f>
-        <v>0.26</v>
+        <f>$D$2</f>
+        <v>0.26400000000000001</v>
       </c>
       <c r="F2">
-        <f t="shared" si="0"/>
-        <v>0.26</v>
+        <f t="shared" ref="F2:AE2" si="0">$D$2</f>
+        <v>0.26400000000000001</v>
       </c>
       <c r="G2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="P2">
-        <f>$B$2</f>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
       <c r="Q2">
-        <f>$B$2</f>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
       <c r="R2">
-        <f t="shared" ref="R2:V2" si="1">$B$2</f>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
       <c r="S2">
-        <f t="shared" si="1"/>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
       <c r="T2">
-        <f t="shared" si="1"/>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
       <c r="U2">
-        <f t="shared" si="1"/>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
       <c r="V2">
-        <f t="shared" si="1"/>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
       <c r="W2">
-        <f>$B$2</f>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
       <c r="X2">
-        <f>$B$2</f>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
       <c r="Y2">
-        <f t="shared" ref="Y2:AA2" si="2">$B$2</f>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
       <c r="Z2">
-        <f t="shared" si="2"/>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
       <c r="AA2">
-        <f t="shared" si="2"/>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
       <c r="AB2">
-        <f>$B$2</f>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
       <c r="AC2">
-        <f>$B$2</f>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
       <c r="AD2">
-        <f t="shared" ref="AD2:AM2" si="3">$B$2</f>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
       <c r="AE2">
-        <f t="shared" si="3"/>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.26400000000000001</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D785AEF-AD64-40F1-9CCF-B92F11603A70}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010A30CC-9974-4F91-9602-198D4EB07E05}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC8F397C-BC1B-4086-B3BE-CA81AA18B242}"/>
 </file>